--- a/Proyecto Interno/interno/output/lista alimentos/alimentos_total_ciudad.xlsx
+++ b/Proyecto Interno/interno/output/lista alimentos/alimentos_total_ciudad.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f8f89820ab55adc2/Escritorio/Least-cost-diets-and-affordability/Proyecto Interno/interno/output/lista alimentos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_B99231273C496BF5641522EEF75D04AF1A5888DB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D0DFFFC6-5567-438D-8BB2-7FFD67C4870A}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_B89231273C0965BB14B636922F5F00BDDAD98242" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{332D7D82-E421-4179-9324-12F241816A80}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="132">
   <si>
     <t>sipsa_name</t>
   </si>
@@ -82,6 +82,9 @@
     <t>Bagre rayado en postas congelado</t>
   </si>
   <si>
+    <t>Banano bocadillo</t>
+  </si>
+  <si>
     <t>Berenjena</t>
   </si>
   <si>
@@ -166,15 +169,6 @@
     <t>Cebolla junca</t>
   </si>
   <si>
-    <t>Chocolate amargo</t>
-  </si>
-  <si>
-    <t>Chocolate dulce</t>
-  </si>
-  <si>
-    <t>Chocolate instantáneo</t>
-  </si>
-  <si>
     <t>Chócolo mazorca</t>
   </si>
   <si>
@@ -193,9 +187,6 @@
     <t>Coliflor</t>
   </si>
   <si>
-    <t>Color (bolsita)</t>
-  </si>
-  <si>
     <t>Corvina, filete congelado nacional</t>
   </si>
   <si>
@@ -226,24 +217,27 @@
     <t>Fríjol enlatado</t>
   </si>
   <si>
+    <t>Fríjol verde en vaina</t>
+  </si>
+  <si>
     <t>Fécula de maíz</t>
   </si>
   <si>
-    <t>Galletas saladas</t>
-  </si>
-  <si>
     <t>Garbanzo importado</t>
   </si>
   <si>
-    <t>Gelatina</t>
-  </si>
-  <si>
     <t>Guanábana</t>
   </si>
   <si>
     <t>Guayaba pera</t>
   </si>
   <si>
+    <t>Gulupa</t>
+  </si>
+  <si>
+    <t>Habichuela</t>
+  </si>
+  <si>
     <t>Harina de trigo</t>
   </si>
   <si>
@@ -256,7 +250,7 @@
     <t>Huevo rojo A</t>
   </si>
   <si>
-    <t>Jugo instantáneo (sobre)</t>
+    <t>Huevo rojo extra</t>
   </si>
   <si>
     <t>Kiwi</t>
@@ -295,12 +289,6 @@
     <t>Maracuyá</t>
   </si>
   <si>
-    <t>Margarina</t>
-  </si>
-  <si>
-    <t>Mayonesa doy pack</t>
-  </si>
-  <si>
     <t>Maíz amarillo cáscara</t>
   </si>
   <si>
@@ -319,9 +307,6 @@
     <t>Melón Cantalup</t>
   </si>
   <si>
-    <t>Mostaza doy pack</t>
-  </si>
-  <si>
     <t>Naranja común</t>
   </si>
   <si>
@@ -331,6 +316,9 @@
     <t>Panela redonda morena</t>
   </si>
   <si>
+    <t>Papa capira</t>
+  </si>
+  <si>
     <t>Papa parda pastusa</t>
   </si>
   <si>
@@ -395,9 +383,6 @@
   </si>
   <si>
     <t>Salmón, filete congelado</t>
-  </si>
-  <si>
-    <t>Salsa de tomate doy pack</t>
   </si>
   <si>
     <t>Sardinas en lata</t>
@@ -764,7 +749,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B136"/>
+  <dimension ref="A1:B131"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.77734375" bestFit="1" customWidth="1"/>
@@ -783,7 +768,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
@@ -791,7 +776,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -799,7 +784,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -807,7 +792,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
@@ -815,7 +800,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
@@ -823,7 +808,7 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
@@ -831,7 +816,7 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
@@ -839,7 +824,7 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
@@ -847,7 +832,7 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
@@ -855,7 +840,7 @@
         <v>11</v>
       </c>
       <c r="B11">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
@@ -863,7 +848,7 @@
         <v>12</v>
       </c>
       <c r="B12">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
@@ -871,7 +856,7 @@
         <v>13</v>
       </c>
       <c r="B13">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
@@ -879,7 +864,7 @@
         <v>14</v>
       </c>
       <c r="B14">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
@@ -887,7 +872,7 @@
         <v>15</v>
       </c>
       <c r="B15">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
@@ -895,7 +880,7 @@
         <v>16</v>
       </c>
       <c r="B16">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
@@ -903,7 +888,7 @@
         <v>17</v>
       </c>
       <c r="B17">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
@@ -911,7 +896,7 @@
         <v>18</v>
       </c>
       <c r="B18">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
@@ -919,7 +904,7 @@
         <v>19</v>
       </c>
       <c r="B19">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
@@ -927,7 +912,7 @@
         <v>20</v>
       </c>
       <c r="B20">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
@@ -935,7 +920,7 @@
         <v>21</v>
       </c>
       <c r="B21">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
@@ -943,7 +928,7 @@
         <v>22</v>
       </c>
       <c r="B22">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
@@ -951,7 +936,7 @@
         <v>23</v>
       </c>
       <c r="B23">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
@@ -959,7 +944,7 @@
         <v>24</v>
       </c>
       <c r="B24">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
@@ -967,7 +952,7 @@
         <v>25</v>
       </c>
       <c r="B25">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
@@ -975,7 +960,7 @@
         <v>26</v>
       </c>
       <c r="B26">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
@@ -983,7 +968,7 @@
         <v>27</v>
       </c>
       <c r="B27">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
@@ -991,7 +976,7 @@
         <v>28</v>
       </c>
       <c r="B28">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
@@ -999,7 +984,7 @@
         <v>29</v>
       </c>
       <c r="B29">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
@@ -1007,7 +992,7 @@
         <v>30</v>
       </c>
       <c r="B30">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
@@ -1015,7 +1000,7 @@
         <v>31</v>
       </c>
       <c r="B31">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
@@ -1023,7 +1008,7 @@
         <v>32</v>
       </c>
       <c r="B32">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
@@ -1031,7 +1016,7 @@
         <v>33</v>
       </c>
       <c r="B33">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
@@ -1039,7 +1024,7 @@
         <v>34</v>
       </c>
       <c r="B34">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
@@ -1047,7 +1032,7 @@
         <v>35</v>
       </c>
       <c r="B35">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
@@ -1055,7 +1040,7 @@
         <v>36</v>
       </c>
       <c r="B36">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
@@ -1063,7 +1048,7 @@
         <v>37</v>
       </c>
       <c r="B37">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
@@ -1071,7 +1056,7 @@
         <v>38</v>
       </c>
       <c r="B38">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
@@ -1079,7 +1064,7 @@
         <v>39</v>
       </c>
       <c r="B39">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
@@ -1087,7 +1072,7 @@
         <v>40</v>
       </c>
       <c r="B40">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
@@ -1095,7 +1080,7 @@
         <v>41</v>
       </c>
       <c r="B41">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
@@ -1103,7 +1088,7 @@
         <v>42</v>
       </c>
       <c r="B42">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
@@ -1111,7 +1096,7 @@
         <v>43</v>
       </c>
       <c r="B43">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
@@ -1119,7 +1104,7 @@
         <v>44</v>
       </c>
       <c r="B44">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
@@ -1127,7 +1112,7 @@
         <v>45</v>
       </c>
       <c r="B45">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
@@ -1135,7 +1120,7 @@
         <v>46</v>
       </c>
       <c r="B46">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
@@ -1143,7 +1128,7 @@
         <v>47</v>
       </c>
       <c r="B47">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
@@ -1151,7 +1136,7 @@
         <v>48</v>
       </c>
       <c r="B48">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
@@ -1159,7 +1144,7 @@
         <v>49</v>
       </c>
       <c r="B49">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
@@ -1167,7 +1152,7 @@
         <v>50</v>
       </c>
       <c r="B50">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
@@ -1175,7 +1160,7 @@
         <v>51</v>
       </c>
       <c r="B51">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
@@ -1183,7 +1168,7 @@
         <v>52</v>
       </c>
       <c r="B52">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
@@ -1191,7 +1176,7 @@
         <v>53</v>
       </c>
       <c r="B53">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
@@ -1199,7 +1184,7 @@
         <v>54</v>
       </c>
       <c r="B54">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
@@ -1207,7 +1192,7 @@
         <v>55</v>
       </c>
       <c r="B55">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
@@ -1215,7 +1200,7 @@
         <v>56</v>
       </c>
       <c r="B56">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
@@ -1223,7 +1208,7 @@
         <v>57</v>
       </c>
       <c r="B57">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
@@ -1231,7 +1216,7 @@
         <v>58</v>
       </c>
       <c r="B58">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
@@ -1239,7 +1224,7 @@
         <v>59</v>
       </c>
       <c r="B59">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
@@ -1247,7 +1232,7 @@
         <v>60</v>
       </c>
       <c r="B60">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
@@ -1255,7 +1240,7 @@
         <v>61</v>
       </c>
       <c r="B61">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
@@ -1263,7 +1248,7 @@
         <v>62</v>
       </c>
       <c r="B62">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
@@ -1271,7 +1256,7 @@
         <v>63</v>
       </c>
       <c r="B63">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
@@ -1279,7 +1264,7 @@
         <v>64</v>
       </c>
       <c r="B64">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
@@ -1287,7 +1272,7 @@
         <v>65</v>
       </c>
       <c r="B65">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
@@ -1295,7 +1280,7 @@
         <v>66</v>
       </c>
       <c r="B66">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
@@ -1303,7 +1288,7 @@
         <v>67</v>
       </c>
       <c r="B67">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
@@ -1311,7 +1296,7 @@
         <v>68</v>
       </c>
       <c r="B68">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
@@ -1319,7 +1304,7 @@
         <v>69</v>
       </c>
       <c r="B69">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
@@ -1327,7 +1312,7 @@
         <v>70</v>
       </c>
       <c r="B70">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
@@ -1335,7 +1320,7 @@
         <v>71</v>
       </c>
       <c r="B71">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
@@ -1343,7 +1328,7 @@
         <v>72</v>
       </c>
       <c r="B72">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
@@ -1351,7 +1336,7 @@
         <v>73</v>
       </c>
       <c r="B73">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
@@ -1359,7 +1344,7 @@
         <v>74</v>
       </c>
       <c r="B74">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
@@ -1367,7 +1352,7 @@
         <v>75</v>
       </c>
       <c r="B75">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
@@ -1375,7 +1360,7 @@
         <v>76</v>
       </c>
       <c r="B76">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
@@ -1383,7 +1368,7 @@
         <v>77</v>
       </c>
       <c r="B77">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
@@ -1391,7 +1376,7 @@
         <v>78</v>
       </c>
       <c r="B78">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
@@ -1399,7 +1384,7 @@
         <v>79</v>
       </c>
       <c r="B79">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
@@ -1407,7 +1392,7 @@
         <v>80</v>
       </c>
       <c r="B80">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.3">
@@ -1415,7 +1400,7 @@
         <v>81</v>
       </c>
       <c r="B81">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.3">
@@ -1423,7 +1408,7 @@
         <v>82</v>
       </c>
       <c r="B82">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.3">
@@ -1431,7 +1416,7 @@
         <v>83</v>
       </c>
       <c r="B83">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.3">
@@ -1439,7 +1424,7 @@
         <v>84</v>
       </c>
       <c r="B84">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.3">
@@ -1447,7 +1432,7 @@
         <v>85</v>
       </c>
       <c r="B85">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.3">
@@ -1455,7 +1440,7 @@
         <v>86</v>
       </c>
       <c r="B86">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.3">
@@ -1463,7 +1448,7 @@
         <v>87</v>
       </c>
       <c r="B87">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.3">
@@ -1471,7 +1456,7 @@
         <v>88</v>
       </c>
       <c r="B88">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.3">
@@ -1479,7 +1464,7 @@
         <v>89</v>
       </c>
       <c r="B89">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.3">
@@ -1487,7 +1472,7 @@
         <v>90</v>
       </c>
       <c r="B90">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.3">
@@ -1495,7 +1480,7 @@
         <v>91</v>
       </c>
       <c r="B91">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.3">
@@ -1503,7 +1488,7 @@
         <v>92</v>
       </c>
       <c r="B92">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.3">
@@ -1511,7 +1496,7 @@
         <v>93</v>
       </c>
       <c r="B93">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.3">
@@ -1519,7 +1504,7 @@
         <v>94</v>
       </c>
       <c r="B94">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.3">
@@ -1527,7 +1512,7 @@
         <v>95</v>
       </c>
       <c r="B95">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.3">
@@ -1535,7 +1520,7 @@
         <v>96</v>
       </c>
       <c r="B96">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.3">
@@ -1543,7 +1528,7 @@
         <v>97</v>
       </c>
       <c r="B97">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.3">
@@ -1551,7 +1536,7 @@
         <v>98</v>
       </c>
       <c r="B98">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.3">
@@ -1559,7 +1544,7 @@
         <v>99</v>
       </c>
       <c r="B99">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.3">
@@ -1567,7 +1552,7 @@
         <v>100</v>
       </c>
       <c r="B100">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.3">
@@ -1575,7 +1560,7 @@
         <v>101</v>
       </c>
       <c r="B101">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.3">
@@ -1583,7 +1568,7 @@
         <v>102</v>
       </c>
       <c r="B102">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.3">
@@ -1591,7 +1576,7 @@
         <v>103</v>
       </c>
       <c r="B103">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.3">
@@ -1599,7 +1584,7 @@
         <v>104</v>
       </c>
       <c r="B104">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.3">
@@ -1607,7 +1592,7 @@
         <v>105</v>
       </c>
       <c r="B105">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.3">
@@ -1615,7 +1600,7 @@
         <v>106</v>
       </c>
       <c r="B106">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.3">
@@ -1623,7 +1608,7 @@
         <v>107</v>
       </c>
       <c r="B107">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.3">
@@ -1631,7 +1616,7 @@
         <v>108</v>
       </c>
       <c r="B108">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.3">
@@ -1639,7 +1624,7 @@
         <v>109</v>
       </c>
       <c r="B109">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.3">
@@ -1647,7 +1632,7 @@
         <v>110</v>
       </c>
       <c r="B110">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.3">
@@ -1655,7 +1640,7 @@
         <v>111</v>
       </c>
       <c r="B111">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.3">
@@ -1663,7 +1648,7 @@
         <v>112</v>
       </c>
       <c r="B112">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.3">
@@ -1671,7 +1656,7 @@
         <v>113</v>
       </c>
       <c r="B113">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.3">
@@ -1679,7 +1664,7 @@
         <v>114</v>
       </c>
       <c r="B114">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.3">
@@ -1687,7 +1672,7 @@
         <v>115</v>
       </c>
       <c r="B115">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.3">
@@ -1695,7 +1680,7 @@
         <v>116</v>
       </c>
       <c r="B116">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.3">
@@ -1703,7 +1688,7 @@
         <v>117</v>
       </c>
       <c r="B117">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.3">
@@ -1711,7 +1696,7 @@
         <v>118</v>
       </c>
       <c r="B118">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.3">
@@ -1719,7 +1704,7 @@
         <v>119</v>
       </c>
       <c r="B119">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.3">
@@ -1727,7 +1712,7 @@
         <v>120</v>
       </c>
       <c r="B120">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.3">
@@ -1735,7 +1720,7 @@
         <v>121</v>
       </c>
       <c r="B121">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.3">
@@ -1743,7 +1728,7 @@
         <v>122</v>
       </c>
       <c r="B122">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.3">
@@ -1751,7 +1736,7 @@
         <v>123</v>
       </c>
       <c r="B123">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.3">
@@ -1759,7 +1744,7 @@
         <v>124</v>
       </c>
       <c r="B124">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.3">
@@ -1767,7 +1752,7 @@
         <v>125</v>
       </c>
       <c r="B125">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.3">
@@ -1775,7 +1760,7 @@
         <v>126</v>
       </c>
       <c r="B126">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.3">
@@ -1783,7 +1768,7 @@
         <v>127</v>
       </c>
       <c r="B127">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.3">
@@ -1791,7 +1776,7 @@
         <v>128</v>
       </c>
       <c r="B128">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.3">
@@ -1799,7 +1784,7 @@
         <v>129</v>
       </c>
       <c r="B129">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.3">
@@ -1807,7 +1792,7 @@
         <v>130</v>
       </c>
       <c r="B130">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.3">
@@ -1815,47 +1800,7 @@
         <v>131</v>
       </c>
       <c r="B131">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A132" t="s">
-        <v>132</v>
-      </c>
-      <c r="B132">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A133" t="s">
-        <v>133</v>
-      </c>
-      <c r="B133">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A134" t="s">
-        <v>134</v>
-      </c>
-      <c r="B134">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A135" t="s">
-        <v>135</v>
-      </c>
-      <c r="B135">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A136" t="s">
-        <v>136</v>
-      </c>
-      <c r="B136">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
